--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5969" uniqueCount="712">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Patient concerné par le document.</t>
+    <t>Ce profil représente  le patient concerné par le document.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1276,6 +1276,263 @@
     <t>PID-5, PID-9</t>
   </si>
   <si>
+    <t>Patient.name.id</t>
+  </si>
+  <si>
+    <t>Patient.name.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.extension:assemblyOrder</t>
+  </si>
+  <si>
+    <t>assemblyOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-assembly-order}
+</t>
+  </si>
+  <si>
+    <t>Preferred display order of name parts</t>
+  </si>
+  <si>
+    <t>A code that represents the preferred display order of the components of this human name.</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>Patient.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>Patient.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>Patient.name.family.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Patient.name.family.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.family.extension:qualifier-family</t>
+  </si>
+  <si>
+    <t>qualifier-family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-qualifier-extension}
+</t>
+  </si>
+  <si>
+    <t>QualifierExtension</t>
+  </si>
+  <si>
+    <t>Extension permettant d'ajouter un qualifier dans les noms et prénoms du patient.
+ - name.family : 
+    - qualifier='BR' pour le nom de naissance (ou nom de famille) : obligatoire si le matricule INS est présent. 
+    - qualifier='CL' pour le nom utilisé (RNIV).
+ - name.given : 
+    - qualifier non utilisé pour la liste des prénoms de l’acte de naissance : obligatoire si le matricule INS est présent.
+    - qualifier='BR' pour le premier prénom extrait de la liste des prénoms de l’acte de naissance : obligatoire si le matricule INS est présent.  
+    - qualifier='CL' pour pour le prénom utilisé (RNIV).</t>
+  </si>
+  <si>
+    <t>Patient.name.family.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
+    <t>Patient.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>Patient.name.given.id</t>
+  </si>
+  <si>
+    <t>Patient.name.given.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.given.extension:qualifier-given</t>
+  </si>
+  <si>
+    <t>qualifier-given</t>
+  </si>
+  <si>
+    <t>Patient.name.given.value</t>
+  </si>
+  <si>
+    <t>Patient.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>Civilités des personnes physiques du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>Patient.name.suffix</t>
+  </si>
+  <si>
+    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>Civilités d'exercice d'un professionnel du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>Patient.name.period</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
+  </si>
+  <si>
     <t>Patient.name:usualName</t>
   </si>
   <si>
@@ -1295,195 +1552,37 @@
     <t>Patient.name:usualName.id</t>
   </si>
   <si>
-    <t>Patient.name.id</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.extension</t>
   </si>
   <si>
-    <t>Patient.name.extension</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.use</t>
   </si>
   <si>
-    <t>Patient.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
     <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
   </si>
   <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.text</t>
   </si>
   <si>
-    <t>Patient.name.text</t>
-  </si>
-  <si>
-    <t>Text representation of the full name</t>
-  </si>
-  <si>
-    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
-  </si>
-  <si>
-    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
-  </si>
-  <si>
-    <t>A renderable, unencoded form.</t>
-  </si>
-  <si>
-    <t>HumanName.text</t>
-  </si>
-  <si>
-    <t>./formatted</t>
-  </si>
-  <si>
-    <t>implied by XPN.11</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.family</t>
   </si>
   <si>
-    <t>Patient.name.family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">surname
-</t>
-  </si>
-  <si>
-    <t>Family name (often called 'Surname')</t>
-  </si>
-  <si>
-    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
-  </si>
-  <si>
-    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
-  </si>
-  <si>
-    <t>HumanName.family</t>
-  </si>
-  <si>
-    <t>./part[partType = FAM]</t>
-  </si>
-  <si>
-    <t>XPN.1/FN.1</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.given</t>
   </si>
   <si>
-    <t>Patient.name.given</t>
-  </si>
-  <si>
-    <t>first name
-middle name</t>
-  </si>
-  <si>
-    <t>Given names (not always 'first'). Includes middle names</t>
-  </si>
-  <si>
-    <t>Given name.</t>
-  </si>
-  <si>
-    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
-  </si>
-  <si>
-    <t>HumanName.given</t>
-  </si>
-  <si>
-    <t>./part[partType = GIV]</t>
-  </si>
-  <si>
-    <t>XPN.2 + XPN.3</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.prefix</t>
   </si>
   <si>
-    <t>Patient.name.prefix</t>
-  </si>
-  <si>
-    <t>Parts that come before the name</t>
-  </si>
-  <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
-  </si>
-  <si>
-    <t>HumanName.prefix</t>
-  </si>
-  <si>
-    <t>./part[partType = PFX]</t>
-  </si>
-  <si>
-    <t>XPN.5</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.suffix</t>
   </si>
   <si>
-    <t>Patient.name.suffix</t>
-  </si>
-  <si>
     <t>Parts that come after the name</t>
   </si>
   <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>HumanName.suffix</t>
-  </si>
-  <si>
-    <t>./part[partType = SFX]</t>
-  </si>
-  <si>
-    <t>XPN/4</t>
-  </si>
-  <si>
     <t>Patient.name:usualName.period</t>
-  </si>
-  <si>
-    <t>Patient.name.period</t>
-  </si>
-  <si>
-    <t>Time period when name was/is in use</t>
-  </si>
-  <si>
-    <t>Indicates the period of time when this name was valid for the named person.</t>
-  </si>
-  <si>
-    <t>Allows names to be placed in historical context.</t>
-  </si>
-  <si>
-    <t>HumanName.period</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
-    <t>XPN.13 + XPN.14</t>
   </si>
   <si>
     <t>Patient.name:officialName</t>
@@ -1857,7 +1956,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-core-vs-contact-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelationType</t>
@@ -1869,10 +1968,14 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J11-RelationPatient-CISIS/FHIR/JDV-J11-RelationPatient-CISIS</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanName {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-human-name-document}
+</t>
   </si>
   <si>
     <t>Name of a human - parts and usage</t>
@@ -2052,7 +2155,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document)
 </t>
   </si>
   <si>
@@ -2457,7 +2560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO142"/>
+  <dimension ref="A1:AO160"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.79296875" customWidth="true" bestFit="true"/>
@@ -2470,7 +2573,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="144.640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="102.703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2485,7 +2588,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.0703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="90.21875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>
@@ -5172,7 +5275,7 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>117</v>
@@ -5221,7 +5324,7 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>103</v>
@@ -5287,7 +5390,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>80</v>
@@ -10018,7 +10121,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -12357,11 +12460,9 @@
         <v>397</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12370,7 +12471,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12379,23 +12480,19 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>399</v>
+        <v>102</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>400</v>
+        <v>103</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12443,31 +12540,31 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>387</v>
+        <v>105</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>394</v>
+        <v>106</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12475,21 +12572,21 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>80</v>
@@ -12501,15 +12598,17 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12546,31 +12645,31 @@
         <v>80</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>106</v>
@@ -12590,21 +12689,23 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="D87" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -12616,17 +12717,15 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>109</v>
+        <v>401</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>110</v>
+        <v>402</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12663,16 +12762,16 @@
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>116</v>
@@ -12690,7 +12789,7 @@
         <v>117</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
@@ -12707,10 +12806,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12718,7 +12817,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>88</v>
@@ -12736,16 +12835,16 @@
         <v>168</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O88" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12755,7 +12854,7 @@
         <v>80</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>80</v>
@@ -12772,11 +12871,9 @@
       <c r="X88" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y88" t="s" s="2">
-        <v>412</v>
-      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12794,7 +12891,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12809,7 +12906,7 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>80</v>
@@ -12818,7 +12915,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -12826,10 +12923,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12855,16 +12952,16 @@
         <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -12913,7 +13010,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12928,7 +13025,7 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>80</v>
@@ -12937,7 +13034,7 @@
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -12945,14 +13042,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12974,13 +13071,13 @@
         <v>102</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13030,7 +13127,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13045,7 +13142,7 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>80</v>
@@ -13054,7 +13151,7 @@
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13062,21 +13159,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>437</v>
+        <v>80</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>80</v>
@@ -13085,20 +13182,18 @@
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13147,22 +13242,22 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>441</v>
+        <v>105</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>80</v>
@@ -13171,7 +13266,7 @@
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>443</v>
+        <v>80</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13179,10 +13274,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13190,7 +13285,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>79</v>
@@ -13202,16 +13297,16 @@
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>446</v>
+        <v>193</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>447</v>
+        <v>194</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13250,19 +13345,17 @@
         <v>80</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>448</v>
+        <v>116</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13274,10 +13367,10 @@
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>80</v>
@@ -13286,7 +13379,7 @@
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13294,21 +13387,23 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="D93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -13317,16 +13412,16 @@
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>102</v>
+        <v>435</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13377,7 +13472,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>455</v>
+        <v>116</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13386,13 +13481,13 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>456</v>
+        <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>80</v>
@@ -13401,7 +13496,7 @@
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13409,10 +13504,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13432,21 +13527,19 @@
         <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>296</v>
+        <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>462</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
@@ -13467,7 +13560,7 @@
         <v>80</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>80</v>
+        <v>441</v>
       </c>
       <c r="X94" t="s" s="2">
         <v>80</v>
@@ -13494,7 +13587,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13506,10 +13599,10 @@
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>80</v>
@@ -13518,7 +13611,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>465</v>
+        <v>80</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13526,16 +13619,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13554,20 +13645,18 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>399</v>
+        <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13615,7 +13704,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>387</v>
+        <v>448</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13630,16 +13719,16 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>394</v>
+        <v>449</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13647,10 +13736,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13676,10 +13765,10 @@
         <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>103</v>
+        <v>430</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>104</v>
+        <v>431</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13745,7 +13834,7 @@
         <v>80</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>80</v>
@@ -13762,14 +13851,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13791,14 +13880,12 @@
         <v>109</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -13837,9 +13924,7 @@
       <c r="AB97" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AC97" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
         <v>80</v>
       </c>
@@ -13862,7 +13947,7 @@
         <v>117</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>80</v>
@@ -13879,13 +13964,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>80</v>
@@ -13907,13 +13992,13 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>474</v>
+        <v>435</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>476</v>
+        <v>437</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13973,7 +14058,7 @@
         <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>117</v>
@@ -13996,10 +14081,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>407</v>
+        <v>455</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14007,7 +14092,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>88</v>
@@ -14016,26 +14101,22 @@
         <v>80</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
@@ -14044,7 +14125,7 @@
         <v>80</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>80</v>
@@ -14056,16 +14137,16 @@
         <v>80</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>80</v>
+        <v>441</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>80</v>
@@ -14083,7 +14164,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14095,10 +14176,10 @@
         <v>80</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>80</v>
@@ -14107,7 +14188,7 @@
         <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14115,10 +14196,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14144,17 +14225,13 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>80</v>
       </c>
@@ -14178,13 +14255,13 @@
         <v>80</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14202,13 +14279,13 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>80</v>
@@ -14217,7 +14294,7 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>80</v>
@@ -14226,7 +14303,7 @@
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14234,21 +14311,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>80</v>
@@ -14263,14 +14340,12 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14295,13 +14370,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14319,13 +14394,13 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>80</v>
@@ -14334,7 +14409,7 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>80</v>
@@ -14343,7 +14418,7 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14351,21 +14426,21 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>437</v>
+        <v>80</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>80</v>
@@ -14377,18 +14452,18 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>102</v>
+        <v>296</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
       </c>
@@ -14436,13 +14511,13 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>80</v>
@@ -14451,7 +14526,7 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>80</v>
@@ -14460,7 +14535,7 @@
         <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14468,12 +14543,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C103" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="D103" t="s" s="2">
         <v>80</v>
       </c>
@@ -14494,16 +14571,20 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>102</v>
+        <v>481</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
       </c>
@@ -14551,7 +14632,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>448</v>
+        <v>387</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14566,16 +14647,16 @@
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>450</v>
+        <v>396</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -14583,10 +14664,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>452</v>
+        <v>397</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14597,7 +14678,7 @@
         <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>80</v>
@@ -14606,16 +14687,16 @@
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>453</v>
+        <v>103</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>454</v>
+        <v>104</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14666,22 +14747,22 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>455</v>
+        <v>105</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>80</v>
@@ -14690,7 +14771,7 @@
         <v>80</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -14698,21 +14779,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>459</v>
+        <v>398</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>80</v>
@@ -14721,21 +14802,21 @@
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>296</v>
+        <v>109</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>460</v>
+        <v>110</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
       </c>
@@ -14771,34 +14852,34 @@
         <v>80</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>463</v>
+        <v>116</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>464</v>
+        <v>106</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>80</v>
@@ -14807,7 +14888,7 @@
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>465</v>
+        <v>80</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -14815,10 +14896,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>404</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14826,34 +14907,34 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>485</v>
+        <v>168</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>486</v>
+        <v>405</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>487</v>
+        <v>406</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -14863,7 +14944,7 @@
         <v>80</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>80</v>
@@ -14878,13 +14959,13 @@
         <v>80</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>80</v>
+        <v>487</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>80</v>
+        <v>488</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
@@ -14902,22 +14983,22 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>484</v>
+        <v>410</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>491</v>
+        <v>411</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>80</v>
@@ -14926,7 +15007,7 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>492</v>
+        <v>412</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
@@ -14934,10 +15015,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>493</v>
+        <v>413</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14960,19 +15041,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>494</v>
+        <v>414</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>496</v>
+        <v>416</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>497</v>
+        <v>417</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -14997,13 +15078,13 @@
         <v>80</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>498</v>
+        <v>80</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>80</v>
@@ -15021,7 +15102,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15036,16 +15117,16 @@
         <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>500</v>
+        <v>419</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>502</v>
+        <v>420</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15053,14 +15134,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15079,20 +15160,18 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>504</v>
+        <v>102</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>505</v>
+        <v>423</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>506</v>
+        <v>424</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15140,7 +15219,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>503</v>
+        <v>426</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15155,63 +15234,61 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>509</v>
+        <v>427</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>511</v>
+        <v>428</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>512</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>514</v>
+        <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
       </c>
@@ -15259,13 +15336,13 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>513</v>
+        <v>448</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>80</v>
@@ -15274,16 +15351,16 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>519</v>
+        <v>449</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15291,10 +15368,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15314,23 +15391,19 @@
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>235</v>
+        <v>457</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15378,7 +15451,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15387,13 +15460,13 @@
         <v>79</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>239</v>
+        <v>462</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>80</v>
@@ -15402,7 +15475,7 @@
         <v>80</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>240</v>
+        <v>463</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>80</v>
@@ -15410,10 +15483,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>523</v>
+        <v>464</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15424,7 +15497,7 @@
         <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>80</v>
@@ -15433,21 +15506,19 @@
         <v>80</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>524</v>
+        <v>494</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>525</v>
+        <v>466</v>
       </c>
       <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>526</v>
-      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15471,11 +15542,13 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -15493,13 +15566,13 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>523</v>
+        <v>469</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>80</v>
@@ -15508,16 +15581,16 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>528</v>
+        <v>470</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>529</v>
+        <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>530</v>
+        <v>471</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15525,10 +15598,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>531</v>
+        <v>472</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15548,22 +15621,20 @@
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>532</v>
+        <v>296</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>533</v>
+        <v>473</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>536</v>
+        <v>475</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -15612,7 +15683,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>531</v>
+        <v>476</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15627,16 +15698,16 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>537</v>
+        <v>477</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>538</v>
+        <v>478</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -15644,12 +15715,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>539</v>
+        <v>496</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C113" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="D113" t="s" s="2">
         <v>80</v>
       </c>
@@ -15667,22 +15740,22 @@
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>541</v>
+        <v>498</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>542</v>
+        <v>499</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>543</v>
+        <v>391</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>544</v>
+        <v>392</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -15731,7 +15804,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>539</v>
+        <v>387</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15746,16 +15819,16 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>545</v>
+        <v>394</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>106</v>
+        <v>395</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>546</v>
+        <v>396</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -15763,10 +15836,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>547</v>
+        <v>500</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>547</v>
+        <v>397</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15777,7 +15850,7 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>80</v>
@@ -15789,20 +15862,16 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>548</v>
+        <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>549</v>
+        <v>103</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>80</v>
       </c>
@@ -15850,25 +15919,25 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>547</v>
+        <v>105</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>554</v>
+        <v>106</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>80</v>
@@ -15882,21 +15951,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>555</v>
+        <v>501</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>555</v>
+        <v>398</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>80</v>
@@ -15908,15 +15977,17 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -15953,31 +16024,31 @@
         <v>80</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>106</v>
@@ -15997,12 +16068,14 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>556</v>
+        <v>502</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C116" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="D116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16011,7 +16084,7 @@
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -16023,13 +16096,13 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>109</v>
+        <v>504</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>193</v>
+        <v>505</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>194</v>
+        <v>506</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16068,14 +16141,16 @@
         <v>80</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC116" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>116</v>
@@ -16110,20 +16185,18 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>557</v>
+        <v>507</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>88</v>
@@ -16132,22 +16205,26 @@
         <v>80</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>559</v>
+        <v>168</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>560</v>
+        <v>405</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
       </c>
@@ -16156,7 +16233,7 @@
         <v>80</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>80</v>
@@ -16171,13 +16248,13 @@
         <v>80</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>80</v>
+        <v>487</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>80</v>
+        <v>488</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>80</v>
@@ -16195,22 +16272,22 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>116</v>
+        <v>410</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>80</v>
@@ -16219,7 +16296,7 @@
         <v>80</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16227,14 +16304,12 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>562</v>
+        <v>508</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>80</v>
       </c>
@@ -16252,19 +16327,23 @@
         <v>80</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>564</v>
+        <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>565</v>
+        <v>414</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>80</v>
       </c>
@@ -16312,22 +16391,22 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>116</v>
+        <v>418</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>80</v>
@@ -16336,7 +16415,7 @@
         <v>80</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>80</v>
@@ -16344,46 +16423,44 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>567</v>
+        <v>509</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>567</v>
+        <v>421</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>568</v>
+        <v>422</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J119" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>569</v>
+        <v>423</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>570</v>
+        <v>424</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>80</v>
       </c>
@@ -16431,22 +16508,22 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>571</v>
+        <v>426</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>191</v>
+        <v>427</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>80</v>
@@ -16455,7 +16532,7 @@
         <v>80</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>80</v>
@@ -16463,18 +16540,18 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>572</v>
+        <v>510</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>572</v>
+        <v>443</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>79</v>
@@ -16486,21 +16563,21 @@
         <v>80</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>573</v>
+        <v>445</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>80</v>
       </c>
@@ -16524,29 +16601,31 @@
         <v>80</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>577</v>
+        <v>80</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AC120" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>572</v>
+        <v>448</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16561,16 +16640,16 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>80</v>
@@ -16578,14 +16657,12 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>581</v>
+        <v>511</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>80</v>
       </c>
@@ -16594,7 +16671,7 @@
         <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>80</v>
@@ -16603,21 +16680,19 @@
         <v>80</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>583</v>
+        <v>457</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>574</v>
+        <v>458</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" t="s" s="2">
-        <v>575</v>
-      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>80</v>
       </c>
@@ -16641,11 +16716,13 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y121" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -16663,7 +16740,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>572</v>
+        <v>461</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16678,16 +16755,16 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>579</v>
+        <v>462</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>580</v>
+        <v>463</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>80</v>
@@ -16695,14 +16772,12 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>585</v>
+        <v>512</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>80</v>
       </c>
@@ -16711,7 +16786,7 @@
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>80</v>
@@ -16720,21 +16795,19 @@
         <v>80</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>587</v>
+        <v>494</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>574</v>
+        <v>466</v>
       </c>
       <c r="N122" s="2"/>
-      <c r="O122" t="s" s="2">
-        <v>575</v>
-      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>80</v>
       </c>
@@ -16758,11 +16831,13 @@
         <v>80</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y122" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -16780,7 +16855,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>572</v>
+        <v>469</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16795,16 +16870,16 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>579</v>
+        <v>470</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>580</v>
+        <v>471</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>80</v>
@@ -16812,10 +16887,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>589</v>
+        <v>513</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>589</v>
+        <v>472</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16835,22 +16910,20 @@
         <v>80</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>388</v>
+        <v>296</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>590</v>
+        <v>473</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>592</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>593</v>
+        <v>475</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -16899,7 +16972,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>589</v>
+        <v>476</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16908,13 +16981,13 @@
         <v>88</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>594</v>
+        <v>477</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>80</v>
@@ -16923,7 +16996,7 @@
         <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>595</v>
+        <v>478</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>80</v>
@@ -16931,10 +17004,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>596</v>
+        <v>514</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>596</v>
+        <v>514</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16957,19 +17030,19 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>597</v>
+        <v>518</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17018,7 +17091,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>596</v>
+        <v>514</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17030,10 +17103,10 @@
         <v>201</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>80</v>
@@ -17042,7 +17115,7 @@
         <v>80</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>80</v>
@@ -17050,10 +17123,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>598</v>
+        <v>523</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>598</v>
+        <v>523</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17073,20 +17146,22 @@
         <v>80</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>599</v>
+        <v>168</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>600</v>
+        <v>524</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O125" t="s" s="2">
-        <v>602</v>
+        <v>527</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17111,13 +17186,13 @@
         <v>80</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>80</v>
+        <v>528</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>80</v>
+        <v>529</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>80</v>
@@ -17135,7 +17210,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>598</v>
+        <v>523</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17150,16 +17225,16 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>603</v>
+        <v>530</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>106</v>
+        <v>531</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>604</v>
+        <v>532</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
@@ -17167,10 +17242,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>605</v>
+        <v>533</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>605</v>
+        <v>533</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17190,20 +17265,22 @@
         <v>80</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>168</v>
+        <v>534</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O126" t="s" s="2">
-        <v>607</v>
+        <v>538</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
@@ -17228,13 +17305,13 @@
         <v>80</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>498</v>
+        <v>80</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>80</v>
@@ -17252,7 +17329,7 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>605</v>
+        <v>533</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17267,27 +17344,27 @@
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>106</v>
+        <v>540</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>608</v>
+        <v>541</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>80</v>
+        <v>542</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17304,23 +17381,25 @@
         <v>80</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>303</v>
+        <v>544</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>610</v>
+        <v>545</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="O127" t="s" s="2">
-        <v>612</v>
+        <v>548</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17369,7 +17448,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17378,13 +17457,13 @@
         <v>88</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>613</v>
+        <v>80</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>614</v>
+        <v>549</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>106</v>
@@ -17393,7 +17472,7 @@
         <v>80</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>615</v>
+        <v>550</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>
@@ -17401,10 +17480,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>616</v>
+        <v>551</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>616</v>
+        <v>551</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17415,7 +17494,7 @@
         <v>78</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>80</v>
@@ -17427,16 +17506,20 @@
         <v>80</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>617</v>
+        <v>235</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
       </c>
@@ -17484,31 +17567,31 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>616</v>
+        <v>551</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>619</v>
+        <v>239</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>80</v>
@@ -17516,10 +17599,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>620</v>
+        <v>553</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>620</v>
+        <v>553</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17530,7 +17613,7 @@
         <v>78</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>80</v>
@@ -17542,19 +17625,17 @@
         <v>80</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>548</v>
+        <v>270</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>621</v>
+        <v>554</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>624</v>
+        <v>556</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>80</v>
@@ -17579,13 +17660,11 @@
         <v>80</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>80</v>
@@ -17603,13 +17682,13 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>620</v>
+        <v>553</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>80</v>
@@ -17618,16 +17697,16 @@
         <v>100</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>625</v>
+        <v>558</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>626</v>
+        <v>559</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>80</v>
@@ -17635,10 +17714,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17661,16 +17740,20 @@
         <v>80</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>102</v>
+        <v>562</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>103</v>
+        <v>563</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>80</v>
       </c>
@@ -17718,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>105</v>
+        <v>561</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17730,19 +17813,19 @@
         <v>80</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AL130" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AL130" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>80</v>
+        <v>568</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>80</v>
@@ -17750,14 +17833,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>628</v>
+        <v>569</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>628</v>
+        <v>569</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17776,18 +17859,20 @@
         <v>80</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>109</v>
+        <v>570</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>110</v>
+        <v>571</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>111</v>
+        <v>572</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>80</v>
       </c>
@@ -17835,7 +17920,7 @@
         <v>80</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>116</v>
+        <v>569</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17847,19 +17932,19 @@
         <v>80</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AL131" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>80</v>
+        <v>576</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>80</v>
@@ -17867,14 +17952,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>629</v>
+        <v>577</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>629</v>
+        <v>577</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17887,25 +17972,25 @@
         <v>80</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>109</v>
+        <v>578</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>112</v>
+        <v>581</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>244</v>
+        <v>582</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>80</v>
@@ -17954,7 +18039,7 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17966,13 +18051,13 @@
         <v>80</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>117</v>
+        <v>583</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>191</v>
+        <v>584</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>80</v>
@@ -17986,10 +18071,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>630</v>
+        <v>585</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>630</v>
+        <v>585</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17997,7 +18082,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>88</v>
@@ -18012,20 +18097,16 @@
         <v>80</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>631</v>
+        <v>103</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>634</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>80</v>
       </c>
@@ -18049,13 +18130,13 @@
         <v>80</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>80</v>
@@ -18073,10 +18154,10 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>630</v>
+        <v>105</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>88</v>
@@ -18085,19 +18166,19 @@
         <v>80</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>635</v>
+        <v>106</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>637</v>
+        <v>80</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>80</v>
@@ -18105,10 +18186,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>638</v>
+        <v>586</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>638</v>
+        <v>586</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18119,7 +18200,7 @@
         <v>78</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>80</v>
@@ -18131,20 +18212,16 @@
         <v>80</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>379</v>
+        <v>109</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>639</v>
+        <v>193</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>80</v>
       </c>
@@ -18180,43 +18257,41 @@
         <v>80</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>638</v>
+        <v>116</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>643</v>
+        <v>80</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>644</v>
+        <v>80</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>645</v>
+        <v>80</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>80</v>
@@ -18224,21 +18299,23 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>646</v>
+        <v>587</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C135" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="D135" t="s" s="2">
-        <v>647</v>
+        <v>80</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>80</v>
@@ -18250,17 +18327,15 @@
         <v>80</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>648</v>
+        <v>589</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>649</v>
+        <v>590</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>80</v>
@@ -18309,7 +18384,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>646</v>
+        <v>116</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18318,22 +18393,22 @@
         <v>79</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>652</v>
+        <v>80</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>653</v>
+        <v>80</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -18341,12 +18416,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C136" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="D136" t="s" s="2">
         <v>80</v>
       </c>
@@ -18364,23 +18441,19 @@
         <v>80</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>655</v>
+        <v>594</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>656</v>
+        <v>595</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>659</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>80</v>
       </c>
@@ -18428,25 +18501,25 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>654</v>
+        <v>116</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>614</v>
+        <v>80</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>660</v>
+        <v>80</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>80</v>
@@ -18460,14 +18533,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>661</v>
+        <v>597</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>661</v>
+        <v>597</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>80</v>
+        <v>598</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18486,19 +18559,19 @@
         <v>89</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>548</v>
+        <v>109</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>662</v>
+        <v>599</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>663</v>
+        <v>600</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>664</v>
+        <v>112</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>665</v>
+        <v>244</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>80</v>
@@ -18547,7 +18620,7 @@
         <v>80</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>661</v>
+        <v>601</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18559,13 +18632,13 @@
         <v>80</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>666</v>
+        <v>191</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>80</v>
@@ -18579,10 +18652,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>667</v>
+        <v>602</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>667</v>
+        <v>602</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18593,7 +18666,7 @@
         <v>78</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>80</v>
@@ -18605,16 +18678,18 @@
         <v>80</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>102</v>
+        <v>270</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>103</v>
+        <v>603</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>104</v>
+        <v>604</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>80</v>
       </c>
@@ -18638,55 +18713,53 @@
         <v>80</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>80</v>
+        <v>606</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="AC138" s="2"/>
       <c r="AD138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>105</v>
+        <v>602</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK138" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AL138" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AL138" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>80</v>
+        <v>610</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>80</v>
@@ -18694,21 +18767,23 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>668</v>
+        <v>611</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="D139" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>80</v>
@@ -18720,18 +18795,18 @@
         <v>80</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>109</v>
+        <v>270</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>110</v>
+        <v>613</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>80</v>
       </c>
@@ -18755,13 +18830,11 @@
         <v>80</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>80</v>
@@ -18779,7 +18852,7 @@
         <v>80</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>116</v>
+        <v>602</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18791,19 +18864,19 @@
         <v>80</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AL139" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AL139" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>80</v>
+        <v>610</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>80</v>
@@ -18811,45 +18884,45 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>669</v>
+        <v>615</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="D140" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>109</v>
+        <v>270</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>244</v>
+        <v>605</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>80</v>
@@ -18874,13 +18947,11 @@
         <v>80</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>80</v>
@@ -18898,7 +18969,7 @@
         <v>80</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>571</v>
+        <v>602</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18910,19 +18981,19 @@
         <v>80</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>191</v>
+        <v>609</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>80</v>
+        <v>610</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>80</v>
@@ -18930,10 +19001,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>670</v>
+        <v>619</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>670</v>
+        <v>619</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18953,21 +19024,23 @@
         <v>80</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>671</v>
+        <v>620</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>672</v>
+        <v>621</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>673</v>
+        <v>622</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>80</v>
       </c>
@@ -19015,31 +19088,31 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>670</v>
+        <v>619</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>253</v>
+        <v>625</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>675</v>
+        <v>626</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>80</v>
@@ -19047,10 +19120,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>676</v>
+        <v>627</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>676</v>
+        <v>627</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19058,10 +19131,10 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>80</v>
@@ -19070,19 +19143,23 @@
         <v>80</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>168</v>
+        <v>515</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>677</v>
+        <v>516</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>80</v>
       </c>
@@ -19106,57 +19183,2169 @@
         <v>80</v>
       </c>
       <c r="X142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO142" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X144" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y142" t="s" s="2">
+      <c r="Y144" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="P147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="P152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="Z142" t="s" s="2">
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K153" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="AA142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
+      <c r="L153" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK142" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AL142" t="s" s="2">
+      <c r="AK153" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AL153" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AM142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO142" t="s" s="2">
+      <c r="AM153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="P154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO160" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5969" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5971" uniqueCount="716">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce profil représente  le patient concerné par le document.</t>
+    <t>Ce profil représente le patient concerné par le document.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1386,27 +1386,29 @@
     <t>Patient.name.family.extension</t>
   </si>
   <si>
+    <t>qualifier='BR' pour le nom de naissance (ou nom de famille) : obligatoire si le matricule INS est présent.| qualifier='CL' pour le nom utilisé (RNIV).</t>
+  </si>
+  <si>
     <t>Patient.name.family.extension:qualifier-family</t>
   </si>
   <si>
     <t>qualifier-family</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-qualifier-extension}
+    <t xml:space="preserve">Extension {iso21090-EN-qualifier}
 </t>
   </si>
   <si>
-    <t>QualifierExtension</t>
-  </si>
-  <si>
-    <t>Extension permettant d'ajouter un qualifier dans les noms et prénoms du patient.
- - name.family : 
-    - qualifier='BR' pour le nom de naissance (ou nom de famille) : obligatoire si le matricule INS est présent. 
-    - qualifier='CL' pour le nom utilisé (RNIV).
- - name.given : 
-    - qualifier non utilisé pour la liste des prénoms de l’acte de naissance : obligatoire si le matricule INS est présent.
-    - qualifier='BR' pour le premier prénom extrait de la liste des prénoms de l’acte de naissance : obligatoire si le matricule INS est présent.  
-    - qualifier='CL' pour pour le prénom utilisé (RNIV).</t>
+    <t>LS | AC | NB | PR | HON | BR | AD | SP | MID | CL | IN | VV</t>
+  </si>
+  <si>
+    <t>A set of codes each of which specifies a certain subcategory of the name part in addition to the main name part type.</t>
+  </si>
+  <si>
+    <t>Used to indicate additional information about the name part and how it should be used.</t>
+  </si>
+  <si>
+    <t>ENXP.qualifier</t>
   </si>
   <si>
     <t>Patient.name.family.value</t>
@@ -1453,6 +1455,10 @@
   </si>
   <si>
     <t>Patient.name.given.extension</t>
+  </si>
+  <si>
+    <t>qualifier non utilisé pour la liste des prénoms de l’acte de naissance : obligatoire si le matricule INS est présent.| qualifier='BR' pour le premier prénom extrait de la liste des prénoms de l’acte de naissance : obligatoire si le matricule INS est présent.| 
+  qualifier='CL' pour pour le prénom utilisé (RNIV).</t>
   </si>
   <si>
     <t>Patient.name.given.extension:qualifier-given</t>
@@ -1956,7 +1962,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-core-vs-contact-role</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-patient-contact-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelationType</t>
@@ -13303,7 +13309,7 @@
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>193</v>
+        <v>433</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>194</v>
@@ -13387,13 +13393,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>432</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>80</v>
@@ -13415,15 +13421,17 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13481,13 +13489,13 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>117</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>80</v>
@@ -13504,10 +13512,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13533,10 +13541,10 @@
         <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13560,7 +13568,7 @@
         <v>80</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="X94" t="s" s="2">
         <v>80</v>
@@ -13587,7 +13595,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13619,14 +13627,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13648,13 +13656,13 @@
         <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13704,7 +13712,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13719,7 +13727,7 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
@@ -13728,7 +13736,7 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13736,10 +13744,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13851,10 +13859,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13880,7 +13888,7 @@
         <v>109</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>193</v>
+        <v>456</v>
       </c>
       <c r="M97" t="s" s="2">
         <v>194</v>
@@ -13964,13 +13972,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>80</v>
@@ -13992,15 +14000,17 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -14058,13 +14068,13 @@
         <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>117</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>80</v>
@@ -14081,10 +14091,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14110,10 +14120,10 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14137,7 +14147,7 @@
         <v>80</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="X99" t="s" s="2">
         <v>80</v>
@@ -14164,7 +14174,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14196,10 +14206,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14225,10 +14235,10 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14258,10 +14268,10 @@
         <v>150</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14279,7 +14289,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14294,7 +14304,7 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>80</v>
@@ -14303,7 +14313,7 @@
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14311,10 +14321,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14340,10 +14350,10 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14373,10 +14383,10 @@
         <v>150</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14394,7 +14404,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14409,7 +14419,7 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>80</v>
@@ -14418,7 +14428,7 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14426,10 +14436,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14455,14 +14465,14 @@
         <v>296</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14511,7 +14521,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14526,7 +14536,7 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>80</v>
@@ -14535,7 +14545,7 @@
         <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14543,13 +14553,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>80</v>
@@ -14571,13 +14581,13 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>391</v>
@@ -14664,7 +14674,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>397</v>
@@ -14779,7 +14789,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>398</v>
@@ -14896,7 +14906,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>404</v>
@@ -14962,10 +14972,10 @@
         <v>264</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
@@ -15015,7 +15025,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>413</v>
@@ -15134,7 +15144,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>421</v>
@@ -15251,14 +15261,14 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15280,13 +15290,13 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15336,7 +15346,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15351,7 +15361,7 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>80</v>
@@ -15360,7 +15370,7 @@
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15368,10 +15378,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15397,10 +15407,10 @@
         <v>102</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15451,7 +15461,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15466,7 +15476,7 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>80</v>
@@ -15475,7 +15485,7 @@
         <v>80</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>80</v>
@@ -15483,10 +15493,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15512,10 +15522,10 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15566,7 +15576,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15581,7 +15591,7 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>80</v>
@@ -15590,7 +15600,7 @@
         <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15598,10 +15608,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15627,14 +15637,14 @@
         <v>296</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -15683,7 +15693,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15698,7 +15708,7 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>80</v>
@@ -15707,7 +15717,7 @@
         <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -15715,13 +15725,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>80</v>
@@ -15743,13 +15753,13 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>391</v>
@@ -15836,7 +15846,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>397</v>
@@ -15951,7 +15961,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>398</v>
@@ -16068,13 +16078,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>398</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>80</v>
@@ -16096,13 +16106,13 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16185,7 +16195,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>404</v>
@@ -16251,10 +16261,10 @@
         <v>264</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>80</v>
@@ -16304,7 +16314,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>413</v>
@@ -16423,7 +16433,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>421</v>
@@ -16540,14 +16550,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16569,13 +16579,13 @@
         <v>102</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16625,7 +16635,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16640,7 +16650,7 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>80</v>
@@ -16649,7 +16659,7 @@
         <v>80</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>80</v>
@@ -16657,10 +16667,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16686,10 +16696,10 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16740,7 +16750,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16755,7 +16765,7 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>80</v>
@@ -16764,7 +16774,7 @@
         <v>80</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>80</v>
@@ -16772,10 +16782,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16801,10 +16811,10 @@
         <v>102</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16855,7 +16865,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16870,7 +16880,7 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>80</v>
@@ -16879,7 +16889,7 @@
         <v>80</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>80</v>
@@ -16887,10 +16897,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16916,14 +16926,14 @@
         <v>296</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -16972,7 +16982,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16987,7 +16997,7 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>80</v>
@@ -16996,7 +17006,7 @@
         <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>80</v>
@@ -17004,10 +17014,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17030,19 +17040,19 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17091,7 +17101,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17103,10 +17113,10 @@
         <v>201</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>80</v>
@@ -17115,7 +17125,7 @@
         <v>80</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>80</v>
@@ -17123,10 +17133,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17152,16 +17162,16 @@
         <v>168</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17189,10 +17199,10 @@
         <v>264</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>80</v>
@@ -17210,7 +17220,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17225,16 +17235,16 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
@@ -17242,10 +17252,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17268,19 +17278,19 @@
         <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
@@ -17329,7 +17339,7 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17344,27 +17354,27 @@
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17387,19 +17397,19 @@
         <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17448,7 +17458,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17463,7 +17473,7 @@
         <v>100</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>106</v>
@@ -17472,7 +17482,7 @@
         <v>80</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>
@@ -17480,10 +17490,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17518,7 +17528,7 @@
         <v>237</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -17567,7 +17577,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17599,10 +17609,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17628,14 +17638,14 @@
         <v>270</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>80</v>
@@ -17664,25 +17674,25 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17697,16 +17707,16 @@
         <v>100</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>80</v>
@@ -17714,10 +17724,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17740,19 +17750,19 @@
         <v>80</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>80</v>
@@ -17801,7 +17811,7 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17816,7 +17826,7 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>106</v>
@@ -17825,7 +17835,7 @@
         <v>80</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>80</v>
@@ -17833,10 +17843,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17859,19 +17869,19 @@
         <v>80</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>80</v>
@@ -17920,7 +17930,7 @@
         <v>80</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17935,7 +17945,7 @@
         <v>100</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>106</v>
@@ -17944,7 +17954,7 @@
         <v>80</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>80</v>
@@ -17952,10 +17962,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17978,19 +17988,19 @@
         <v>80</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>80</v>
@@ -18039,7 +18049,7 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -18051,10 +18061,10 @@
         <v>80</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>106</v>
@@ -18071,10 +18081,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18186,10 +18196,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18299,13 +18309,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>80</v>
@@ -18327,13 +18337,13 @@
         <v>80</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18416,13 +18426,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>80</v>
@@ -18444,13 +18454,13 @@
         <v>80</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18533,14 +18543,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18562,10 +18572,10 @@
         <v>109</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>112</v>
@@ -18620,7 +18630,7 @@
         <v>80</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18652,10 +18662,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18681,14 +18691,14 @@
         <v>270</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>80</v>
@@ -18716,16 +18726,16 @@
         <v>150</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AC138" s="2"/>
       <c r="AD138" t="s" s="2">
@@ -18735,7 +18745,7 @@
         <v>115</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18750,7 +18760,7 @@
         <v>100</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>106</v>
@@ -18759,7 +18769,7 @@
         <v>80</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>80</v>
@@ -18767,13 +18777,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>80</v>
@@ -18798,14 +18808,14 @@
         <v>270</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>80</v>
@@ -18834,7 +18844,7 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>80</v>
@@ -18852,7 +18862,7 @@
         <v>80</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18867,7 +18877,7 @@
         <v>100</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>106</v>
@@ -18876,7 +18886,7 @@
         <v>80</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>80</v>
@@ -18884,13 +18894,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>80</v>
@@ -18915,14 +18925,14 @@
         <v>270</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>80</v>
@@ -18951,7 +18961,7 @@
       </c>
       <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>80</v>
@@ -18969,7 +18979,7 @@
         <v>80</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18984,7 +18994,7 @@
         <v>100</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>106</v>
@@ -18993,7 +19003,7 @@
         <v>80</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>80</v>
@@ -19001,10 +19011,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19027,19 +19037,19 @@
         <v>80</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>80</v>
@@ -19088,7 +19098,7 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -19103,7 +19113,7 @@
         <v>100</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>80</v>
@@ -19112,7 +19122,7 @@
         <v>80</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>80</v>
@@ -19120,10 +19130,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19146,19 +19156,19 @@
         <v>80</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>80</v>
@@ -19207,7 +19217,7 @@
         <v>80</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -19219,10 +19229,10 @@
         <v>201</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>80</v>
@@ -19231,7 +19241,7 @@
         <v>80</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>80</v>
@@ -19239,10 +19249,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19265,17 +19275,17 @@
         <v>80</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>80</v>
@@ -19324,7 +19334,7 @@
         <v>80</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -19339,7 +19349,7 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>106</v>
@@ -19348,7 +19358,7 @@
         <v>80</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>80</v>
@@ -19356,10 +19366,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19385,14 +19395,14 @@
         <v>168</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>80</v>
@@ -19420,10 +19430,10 @@
         <v>264</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>80</v>
@@ -19441,7 +19451,7 @@
         <v>80</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19456,7 +19466,7 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>106</v>
@@ -19465,7 +19475,7 @@
         <v>80</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>80</v>
@@ -19473,10 +19483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19502,14 +19512,14 @@
         <v>303</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>80</v>
@@ -19558,7 +19568,7 @@
         <v>80</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19567,13 +19577,13 @@
         <v>88</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>106</v>
@@ -19582,7 +19592,7 @@
         <v>80</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>80</v>
@@ -19590,10 +19600,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19619,10 +19629,10 @@
         <v>296</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19673,7 +19683,7 @@
         <v>80</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19688,7 +19698,7 @@
         <v>100</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>106</v>
@@ -19705,10 +19715,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19731,19 +19741,19 @@
         <v>80</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>80</v>
@@ -19792,7 +19802,7 @@
         <v>80</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19807,10 +19817,10 @@
         <v>100</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>80</v>
@@ -19824,10 +19834,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19939,10 +19949,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20056,14 +20066,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20085,10 +20095,10 @@
         <v>109</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>112</v>
@@ -20143,7 +20153,7 @@
         <v>80</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -20175,10 +20185,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20204,16 +20214,16 @@
         <v>270</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>80</v>
@@ -20262,7 +20272,7 @@
         <v>80</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>88</v>
@@ -20277,16 +20287,16 @@
         <v>100</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>80</v>
@@ -20294,10 +20304,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20323,16 +20333,16 @@
         <v>379</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>80</v>
@@ -20381,7 +20391,7 @@
         <v>80</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -20396,16 +20406,16 @@
         <v>100</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>80</v>
@@ -20413,14 +20423,14 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -20439,16 +20449,16 @@
         <v>80</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -20498,7 +20508,7 @@
         <v>80</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20513,7 +20523,7 @@
         <v>100</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>106</v>
@@ -20522,7 +20532,7 @@
         <v>80</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>80</v>
@@ -20530,10 +20540,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20556,19 +20566,19 @@
         <v>89</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>80</v>
@@ -20617,7 +20627,7 @@
         <v>80</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20632,10 +20642,10 @@
         <v>100</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>80</v>
@@ -20649,10 +20659,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20675,19 +20685,19 @@
         <v>89</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>80</v>
@@ -20736,7 +20746,7 @@
         <v>80</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20751,7 +20761,7 @@
         <v>100</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>106</v>
@@ -20768,10 +20778,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20883,10 +20893,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21000,14 +21010,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21029,10 +21039,10 @@
         <v>109</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>112</v>
@@ -21087,7 +21097,7 @@
         <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -21119,10 +21129,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21145,16 +21155,16 @@
         <v>89</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21204,7 +21214,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>88</v>
@@ -21228,7 +21238,7 @@
         <v>80</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>80</v>
@@ -21236,10 +21246,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21265,10 +21275,10 @@
         <v>168</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21298,10 +21308,10 @@
         <v>264</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>80</v>
@@ -21319,7 +21329,7 @@
         <v>80</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>88</v>
@@ -21334,7 +21344,7 @@
         <v>100</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>106</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-fhir-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
